--- a/.pic/Labs/lab_07_dp/fig_02.xlsx
+++ b/.pic/Labs/lab_07_dp/fig_02.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\voult\Desktop\APS\technical\Labs\Pic\lab_06_dp\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3D48AE3-1397-40FC-AE33-19591A275236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="7140" yWindow="1605" windowWidth="28800" windowHeight="18090" xr2:uid="{E12AB8BA-719F-44C2-A574-EE6DF0DD5D58}"/>
+    <workbookView xWindow="7140" yWindow="1608" windowWidth="28800" windowHeight="17496"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,54 +45,26 @@
     <t>EF</t>
   </si>
   <si>
-    <t>В каком порядке в файле должны идти байты, чтобы инструкция считалась правильно</t>
+    <t>File line number (memory address where the $readmemh function loads this byte)</t>
   </si>
   <si>
-    <t>адрес в памяти, 
-где должен располагаться 
-этот байт</t>
+    <t>Byte value</t>
   </si>
   <si>
-    <t>Значение 
-байта</t>
+    <t>Memory address where this byte should be located</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">№ строки файла
-(адрес в памяти, куда функция </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>$readmemh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> считает этот байт)</t>
-    </r>
+    <t>The order in which the bytes should appear in the file for the instruction to be read correctly</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="00"/>
+    <numFmt numFmtId="164" formatCode="00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,14 +81,6 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-      <charset val="204"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -275,7 +233,7 @@
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -284,7 +242,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -293,28 +251,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -650,38 +608,38 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C7F0DFB-9938-4A75-9C31-9E599C8FA3BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>0</v>
       </c>
@@ -695,7 +653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -709,7 +667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>2</v>
       </c>
@@ -723,7 +681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -737,7 +695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>4</v>
       </c>
@@ -751,7 +709,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>5</v>
       </c>
@@ -765,7 +723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>6</v>
       </c>
@@ -779,7 +737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>7</v>
       </c>
@@ -793,7 +751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>8</v>
       </c>
@@ -807,7 +765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>9</v>
       </c>
@@ -821,7 +779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>10</v>
       </c>
@@ -835,7 +793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>11</v>
       </c>
@@ -849,22 +807,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="2"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="2"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="2"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="2"/>
       <c r="C17" s="1"/>
